--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2024_metropolitana.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:09</t>
+    <t xml:space="preserve">2026-09-24 01:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1004,13 +1004,13 @@
         <v>52</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.12</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="22">
@@ -1030,7 +1030,7 @@
         <v>-0.13</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0.11</v>
@@ -1053,7 +1053,7 @@
         <v>-0.53</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>-0.13</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2024_metropolitana.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:58</t>
+    <t xml:space="preserve">2026-10-01 23:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2024_metropolitana.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:19</t>
+    <t xml:space="preserve">2026-10-05 20:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
